--- a/inputs/input_multiple.xlsx
+++ b/inputs/input_multiple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Profesh\Forward Edge AI\Treasury AI\single-finding-fix\mdl-backend-demo\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16C2E7A-13D8-4851-8293-C2D5D7762681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F40DB29-6F09-43A8-8345-D1AFB6E94A1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28185" yWindow="1485" windowWidth="23175" windowHeight="14055" xr2:uid="{72F4E804-3F27-4A25-B0E1-689D681CEDC7}"/>
+    <workbookView xWindow="14085" yWindow="1230" windowWidth="23175" windowHeight="14055" xr2:uid="{72F4E804-3F27-4A25-B0E1-689D681CEDC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>EIN</t>
   </si>
@@ -63,13 +63,16 @@
   </si>
   <si>
     <t>City of West Haven, CT</t>
+  </si>
+  <si>
+    <t>State of Ohio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +99,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -124,7 +133,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -136,6 +145,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53CE356D-F547-4C03-B419-CF0B195CD08D}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -553,6 +563,17 @@
         <v>3</v>
       </c>
     </row>
+    <row r="8" spans="1:3" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>311334820</v>
+      </c>
+      <c r="B8" s="2">
+        <v>2024</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
